--- a/uploads/Seating_Testing.xlsx
+++ b/uploads/Seating_Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1293DC45-6382-4BBE-8863-DD1A436C0D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1308DCCF-251D-413A-8B0B-4EF1A62C1411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,10 +117,6 @@
     </r>
   </si>
   <si>
-    <t>GUJARAT TECHNOLOGICAL UNIVERSITY GOVERNMENT POLYTECHNIC, AHMEDABAD
-SEATING ARRANGEMENT                                                                                        FOURTH &amp; SIXTH SEMESTER                                                                 DATE:                        12 sept 2026                                              TIME:                10.30 AM TO 1.00 PM</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -188,6 +184,10 @@
   </si>
   <si>
     <t>10101 Q EC</t>
+  </si>
+  <si>
+    <t>GUJARAT TECHNOLOGICAL UNIVERSITY GOVERNMENT POLYTECHNIC, AHMEDABAD
+SEATING ARRANGEMENT                                                                                        FOURTH &amp; SIXTH SEMESTER                                                                 DATE:                        10 sept 2026                                              TIME:                10.30 AM TO 1.00 PM</t>
   </si>
 </sst>
 </file>
@@ -906,7 +906,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="36"/>
@@ -1049,7 +1049,9 @@
       <c r="B7" s="8">
         <v>226178307016</v>
       </c>
-      <c r="C7" s="8"/>
+      <c r="C7" s="8">
+        <v>246171063009</v>
+      </c>
       <c r="D7" s="8">
         <v>236170307002</v>
       </c>
@@ -1117,10 +1119,10 @@
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
       <c r="L10" s="26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M10" s="37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N10" s="23">
         <v>30</v>
@@ -1207,10 +1209,10 @@
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
       <c r="L14" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="25" t="s">
         <v>11</v>
-      </c>
-      <c r="M14" s="25" t="s">
-        <v>12</v>
       </c>
       <c r="N14" s="22">
         <v>30</v>
@@ -1299,10 +1301,10 @@
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
       <c r="L18" s="26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M18" s="31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N18" s="23">
         <v>14</v>
@@ -1371,10 +1373,10 @@
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
       <c r="L21" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="M21" s="28" t="s">
         <v>14</v>
-      </c>
-      <c r="M21" s="28" t="s">
-        <v>15</v>
       </c>
       <c r="N21" s="22">
         <v>30</v>

--- a/uploads/Seating_Testing.xlsx
+++ b/uploads/Seating_Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1308DCCF-251D-413A-8B0B-4EF1A62C1411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E448649-265E-41A2-8116-8F4579347C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -500,24 +500,78 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -529,60 +583,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -905,39 +905,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
     </row>
     <row r="2" spans="1:14" ht="39.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="34"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="24"/>
       <c r="L2" s="2" t="s">
         <v>2</v>
       </c>
@@ -949,7 +949,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40">
+      <c r="A3" s="34">
         <v>41046307</v>
       </c>
       <c r="B3" s="4">
@@ -968,18 +968,18 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
-      <c r="L3" s="48" t="s">
+      <c r="L3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="48" t="s">
+      <c r="M3" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="46">
+      <c r="N3" s="40">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="4">
         <v>246171063006</v>
       </c>
@@ -994,9 +994,9 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="47"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="41"/>
     </row>
     <row r="5" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
@@ -1015,7 +1015,7 @@
       <c r="N5" s="7"/>
     </row>
     <row r="6" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38">
+      <c r="A6" s="32">
         <v>4360709</v>
       </c>
       <c r="B6" s="8">
@@ -1034,18 +1034,18 @@
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
-      <c r="L6" s="44" t="s">
+      <c r="L6" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="44" t="s">
+      <c r="M6" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="42">
+      <c r="N6" s="36">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
+      <c r="A7" s="33"/>
       <c r="B7" s="8">
         <v>226178307016</v>
       </c>
@@ -1062,12 +1062,12 @@
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="43"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="37"/>
     </row>
     <row r="8" spans="1:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="39"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
@@ -1078,9 +1078,9 @@
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="43"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="37"/>
     </row>
     <row r="9" spans="1:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
@@ -1099,7 +1099,7 @@
       <c r="N9" s="19"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="23">
+      <c r="A10" s="27">
         <v>4361905</v>
       </c>
       <c r="B10" s="17">
@@ -1118,18 +1118,18 @@
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
-      <c r="L10" s="26" t="s">
+      <c r="L10" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="M10" s="37" t="s">
+      <c r="M10" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="27">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="23"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="12">
         <v>236170319039</v>
       </c>
@@ -1146,12 +1146,12 @@
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="23"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="27"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="12">
         <v>236170319062</v>
       </c>
@@ -1168,9 +1168,9 @@
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="24"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="28"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
@@ -1189,7 +1189,7 @@
       <c r="N13" s="13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="44">
         <v>4361905</v>
       </c>
       <c r="B14" s="12">
@@ -1208,18 +1208,18 @@
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
-      <c r="L14" s="25" t="s">
+      <c r="L14" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="25" t="s">
+      <c r="M14" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="N14" s="22">
+      <c r="N14" s="44">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="23"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="12">
         <v>236170319110</v>
       </c>
@@ -1236,12 +1236,12 @@
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="23"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="27"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="23"/>
+      <c r="A16" s="27"/>
       <c r="B16" s="21">
         <v>236170319130</v>
       </c>
@@ -1258,9 +1258,9 @@
       <c r="I16" s="21"/>
       <c r="J16" s="21"/>
       <c r="K16" s="21"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="23"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="27"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
@@ -1279,7 +1279,7 @@
       <c r="N17" s="9"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="23">
+      <c r="A18" s="27">
         <v>4360203</v>
       </c>
       <c r="B18" s="17">
@@ -1300,18 +1300,18 @@
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
-      <c r="L18" s="26" t="s">
+      <c r="L18" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="31" t="s">
+      <c r="M18" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="N18" s="23">
+      <c r="N18" s="27">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
+      <c r="A19" s="28"/>
       <c r="B19" s="12">
         <v>246178302040</v>
       </c>
@@ -1330,9 +1330,9 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="24"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="28"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
@@ -1351,7 +1351,7 @@
       <c r="N20" s="13"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="22">
+      <c r="A21" s="44">
         <v>4360904</v>
       </c>
       <c r="B21" s="12">
@@ -1372,18 +1372,18 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
-      <c r="L21" s="25" t="s">
+      <c r="L21" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="M21" s="28" t="s">
+      <c r="M21" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="N21" s="22">
+      <c r="N21" s="44">
         <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
+      <c r="A22" s="27"/>
       <c r="B22" s="12">
         <v>236170309003</v>
       </c>
@@ -1402,12 +1402,12 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="23"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="47"/>
+      <c r="N22" s="27"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
+      <c r="A23" s="28"/>
       <c r="B23" s="12">
         <v>236170309025</v>
       </c>
@@ -1426,12 +1426,24 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="24"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="L21:L23"/>
+    <mergeCell ref="M21:M23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:M16"/>
+    <mergeCell ref="N14:N16"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A10:A12"/>
@@ -1446,18 +1458,6 @@
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="L3:L4"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="L21:L23"/>
-    <mergeCell ref="M21:M23"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:M16"/>
-    <mergeCell ref="N14:N16"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="54" orientation="landscape" r:id="rId1"/>
